--- a/service/TestService/config/xlsx/公共参数.xlsx
+++ b/service/TestService/config/xlsx/公共参数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\Development\CrystalNet\CrystalNet\service\TestService\config\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B774366D-9C1F-493D-83EA-968393995DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DFE68B-D19D-4538-AE95-F0DA2B519023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1020,10 +1020,10 @@
         <v>64</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
         <v>65</v>
